--- a/tests/3D_loop_cond_base/input_template.xlsx
+++ b/tests/3D_loop_cond_base/input_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlasmaArc\simulations\3D_loop_cond_base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlasmaArc\tests\3D_loop_cond_base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2681C8-2D9E-4CFC-9760-9D7841987FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2FDACA-EF59-4F38-850B-1686826996AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="1275" windowWidth="18000" windowHeight="9360" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="element_types" sheetId="1" r:id="rId1"/>
@@ -1278,7 +1278,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
@@ -1355,6 +1355,77 @@
       </c>
       <c r="W1" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tests/3D_loop_cond_base/input_template.xlsx
+++ b/tests/3D_loop_cond_base/input_template.xlsx
@@ -1,30 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlasmaArc\tests\3D_loop_cond_base\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2FDACA-EF59-4F38-850B-1686826996AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="8"/>
   </bookViews>
   <sheets>
-    <sheet name="element_types" sheetId="1" r:id="rId1"/>
-    <sheet name="cp" sheetId="2" r:id="rId2"/>
-    <sheet name="cpcyc" sheetId="3" r:id="rId3"/>
-    <sheet name="materials" sheetId="4" r:id="rId4"/>
-    <sheet name="real_constants" sheetId="5" r:id="rId5"/>
-    <sheet name="solver_settings" sheetId="6" r:id="rId6"/>
-    <sheet name="time_parameters" sheetId="7" r:id="rId7"/>
-    <sheet name="cell_data" sheetId="8" r:id="rId8"/>
-    <sheet name="point_data" sheetId="9" r:id="rId9"/>
-    <sheet name="transient_analysis" sheetId="10" r:id="rId10"/>
+    <sheet r:id="rId1" sheetId="1" name="element_types"/>
+    <sheet r:id="rId2" sheetId="2" name="cp"/>
+    <sheet r:id="rId3" sheetId="3" name="cpcyc"/>
+    <sheet r:id="rId4" sheetId="4" name="materials"/>
+    <sheet r:id="rId5" sheetId="5" name="real_constants"/>
+    <sheet r:id="rId6" sheetId="6" name="solver_settings"/>
+    <sheet r:id="rId7" sheetId="7" name="time_parameters"/>
+    <sheet r:id="rId8" sheetId="8" name="elem"/>
+    <sheet r:id="rId9" sheetId="9" name="node"/>
+    <sheet r:id="rId10" sheetId="10" name="transient_analysis"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -355,14 +349,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.000000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.00000E+00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,6 +366,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -404,54 +403,89 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="25">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -462,10 +496,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -503,71 +537,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -595,7 +629,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -618,11 +652,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -631,13 +665,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -647,7 +681,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -656,7 +690,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -665,7 +699,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -673,10 +707,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -741,23 +775,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="10" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="14.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -776,100 +814,99 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="5">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="C2" s="5">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="5">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>3</v>
       </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>4</v>
       </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="10" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="22.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="13" width="16.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="19.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="13" width="21.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="13" width="21.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -879,111 +916,143 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8">
-        <v>1E-4</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6">
+        <v>0.0001</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="9">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="8">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="B3" s="6">
+        <v>0.0002</v>
+      </c>
+      <c r="C3" s="5">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="9">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="3"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="3"/>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="3"/>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="8"/>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="10"/>
-      <c r="F8" s="9"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="11"/>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="10"/>
-      <c r="F10" s="9"/>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="5"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="5"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="5"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -991,42 +1060,57 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="5"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="5"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="5"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1034,58 +1118,68 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="16" width="14.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="7.147857142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="5"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1093,178 +1187,189 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="10" width="20.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="22" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="5">
         <v>21</v>
       </c>
-      <c r="B2" s="12">
-        <v>1</v>
-      </c>
-      <c r="C2" s="12">
-        <v>1</v>
-      </c>
-      <c r="D2" s="12">
-        <v>1</v>
-      </c>
-      <c r="E2" s="12">
-        <v>0</v>
-      </c>
-      <c r="F2" s="12">
-        <v>0</v>
-      </c>
-      <c r="G2" s="12">
-        <v>0</v>
-      </c>
-      <c r="H2" s="12">
-        <v>0</v>
-      </c>
-      <c r="I2" s="12">
-        <v>0</v>
-      </c>
-      <c r="J2" s="12">
-        <v>0</v>
-      </c>
-      <c r="K2" s="12">
-        <v>0</v>
-      </c>
-      <c r="L2" s="12">
-        <v>0</v>
-      </c>
-      <c r="M2" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="B2" s="23">
+        <v>1</v>
+      </c>
+      <c r="C2" s="23">
+        <v>1</v>
+      </c>
+      <c r="D2" s="23">
+        <v>1</v>
+      </c>
+      <c r="E2" s="23">
+        <v>0</v>
+      </c>
+      <c r="F2" s="23">
+        <v>0</v>
+      </c>
+      <c r="G2" s="23">
+        <v>0</v>
+      </c>
+      <c r="H2" s="23">
+        <v>0</v>
+      </c>
+      <c r="I2" s="23">
+        <v>0</v>
+      </c>
+      <c r="J2" s="23">
+        <v>0</v>
+      </c>
+      <c r="K2" s="23">
+        <v>0</v>
+      </c>
+      <c r="L2" s="23">
+        <v>0</v>
+      </c>
+      <c r="M2" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="5">
         <v>23</v>
       </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="12">
-        <v>1</v>
-      </c>
-      <c r="D3" s="12">
-        <v>1</v>
-      </c>
-      <c r="E3" s="12">
-        <v>0</v>
-      </c>
-      <c r="F3" s="12">
-        <v>0</v>
-      </c>
-      <c r="G3" s="12">
-        <v>0</v>
-      </c>
-      <c r="H3" s="12">
-        <v>0</v>
-      </c>
-      <c r="I3" s="12">
-        <v>0</v>
-      </c>
-      <c r="J3" s="12">
-        <v>0</v>
-      </c>
-      <c r="K3" s="12">
-        <v>0</v>
-      </c>
-      <c r="L3" s="12">
-        <v>0</v>
-      </c>
-      <c r="M3" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="B3" s="23">
+        <v>1</v>
+      </c>
+      <c r="C3" s="23">
+        <v>1</v>
+      </c>
+      <c r="D3" s="23">
+        <v>1</v>
+      </c>
+      <c r="E3" s="23">
+        <v>0</v>
+      </c>
+      <c r="F3" s="23">
+        <v>0</v>
+      </c>
+      <c r="G3" s="23">
+        <v>0</v>
+      </c>
+      <c r="H3" s="23">
+        <v>0</v>
+      </c>
+      <c r="I3" s="23">
+        <v>0</v>
+      </c>
+      <c r="J3" s="23">
+        <v>0</v>
+      </c>
+      <c r="K3" s="23">
+        <v>0</v>
+      </c>
+      <c r="L3" s="23">
+        <v>0</v>
+      </c>
+      <c r="M3" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="5">
         <v>24</v>
       </c>
-      <c r="B4" s="12">
-        <v>1</v>
-      </c>
-      <c r="C4" s="12">
-        <v>1</v>
-      </c>
-      <c r="D4" s="12">
-        <v>1</v>
-      </c>
-      <c r="E4" s="12">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F4" s="12">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="G4" s="12">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H4" s="12">
-        <v>0</v>
-      </c>
-      <c r="I4" s="12">
-        <v>0</v>
-      </c>
-      <c r="J4" s="12">
-        <v>0</v>
-      </c>
-      <c r="K4" s="12">
-        <v>0</v>
-      </c>
-      <c r="L4" s="12">
-        <v>0</v>
-      </c>
-      <c r="M4" s="12">
+      <c r="B4" s="23">
+        <v>1</v>
+      </c>
+      <c r="C4" s="23">
+        <v>1</v>
+      </c>
+      <c r="D4" s="23">
+        <v>1</v>
+      </c>
+      <c r="E4" s="23">
+        <v>1e-9</v>
+      </c>
+      <c r="F4" s="23">
+        <v>1e-9</v>
+      </c>
+      <c r="G4" s="23">
+        <v>1e-9</v>
+      </c>
+      <c r="H4" s="23">
+        <v>0</v>
+      </c>
+      <c r="I4" s="23">
+        <v>0</v>
+      </c>
+      <c r="J4" s="23">
+        <v>0</v>
+      </c>
+      <c r="K4" s="23">
+        <v>0</v>
+      </c>
+      <c r="L4" s="23">
+        <v>0</v>
+      </c>
+      <c r="M4" s="23">
         <v>0</v>
       </c>
     </row>
@@ -1274,157 +1379,177 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="23" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="10" width="21.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0</v>
+      </c>
+      <c r="W2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1434,279 +1559,279 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="13" width="34.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="20" width="12.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="19" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="6">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B4" s="18">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="6">
-        <v>1E-10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B6" s="18">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="6">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B9" s="18">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="6">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B12" s="18">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="5">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="6">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B15" s="18">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="6">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B16" s="18">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B19" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B20" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B22" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B24" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B25" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B26" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B27" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B28" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B29" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B30" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B31" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B32" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="6">
-        <v>9.9999999999999995E-7</v>
+      <c r="B33" s="18">
+        <v>0.000001</v>
       </c>
     </row>
   </sheetData>
@@ -1715,78 +1840,78 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="13" width="23.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="11.290714285714287" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="5">
         <v>1</v>
       </c>
     </row>
@@ -1796,72 +1921,80 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="16" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="16" width="11.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="17"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="17"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="17"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="17"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="17"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="17"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="17"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="17"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1869,97 +2002,110 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="16" width="16.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="17.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="16" width="12.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="5"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="5"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="5"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="5"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="5"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="5"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="5"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="5"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="5"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="5"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="5"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="5"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tests/3D_loop_cond_base/input_template.xlsx
+++ b/tests/3D_loop_cond_base/input_template.xlsx
@@ -1,29 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlasmaArc\tests\3D_loop_cond_base\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7213A11D-5048-493C-AC45-D2838AB72958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="8"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="element_types"/>
-    <sheet r:id="rId2" sheetId="2" name="cp"/>
-    <sheet r:id="rId3" sheetId="3" name="cpcyc"/>
-    <sheet r:id="rId4" sheetId="4" name="materials"/>
-    <sheet r:id="rId5" sheetId="5" name="real_constants"/>
-    <sheet r:id="rId6" sheetId="6" name="solver_settings"/>
-    <sheet r:id="rId7" sheetId="7" name="time_parameters"/>
-    <sheet r:id="rId8" sheetId="8" name="elem"/>
-    <sheet r:id="rId9" sheetId="9" name="node"/>
-    <sheet r:id="rId10" sheetId="10" name="transient_analysis"/>
+    <sheet name="element_types" sheetId="1" r:id="rId1"/>
+    <sheet name="cp" sheetId="2" r:id="rId2"/>
+    <sheet name="cpcyc" sheetId="3" r:id="rId3"/>
+    <sheet name="materials" sheetId="4" r:id="rId4"/>
+    <sheet name="real_constants" sheetId="5" r:id="rId5"/>
+    <sheet name="solver_settings" sheetId="6" r:id="rId6"/>
+    <sheet name="time_parameters" sheetId="7" r:id="rId7"/>
+    <sheet name="elem" sheetId="8" r:id="rId8"/>
+    <sheet name="node" sheetId="9" r:id="rId9"/>
+    <sheet name="transient_analysis" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="105">
   <si>
     <t>time_step_number</t>
   </si>
@@ -184,21 +190,6 @@
     <t>ansys_real_constant</t>
   </si>
   <si>
-    <t>CARE</t>
-  </si>
-  <si>
-    <t>TURN</t>
-  </si>
-  <si>
-    <t>LENG</t>
-  </si>
-  <si>
-    <t>DIRZ</t>
-  </si>
-  <si>
-    <t>FILL</t>
-  </si>
-  <si>
     <t>SC</t>
   </si>
   <si>
@@ -344,12 +335,21 @@
   </si>
   <si>
     <t>SOLID97</t>
+  </si>
+  <si>
+    <t>CPSIGN</t>
+  </si>
+  <si>
+    <t>THK</t>
+  </si>
+  <si>
+    <t>VC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
@@ -403,89 +403,76 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -496,10 +483,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -537,71 +524,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -629,7 +616,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -652,11 +639,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -665,13 +652,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -681,7 +668,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -690,7 +677,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -699,7 +686,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -707,10 +694,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -775,111 +762,107 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="14.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5">
-        <v>21</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>1</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="5">
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>23</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="B3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="4">
         <v>3</v>
       </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="D3" s="4">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="4">
         <v>4</v>
       </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
         <v>0</v>
       </c>
     </row>
@@ -889,24 +872,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="18.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="22.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="16.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="19.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="21.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="13" width="21.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="18.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -916,143 +899,111 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6">
-        <v>0.0001</v>
-      </c>
-      <c r="C2" s="5">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1E-4</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="5">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
-        <v>0.0002</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="B3" s="5">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C3" s="4">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="4"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+    </row>
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="4"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+    </row>
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="4"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+    </row>
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="5"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+    </row>
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="7"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="5"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+    </row>
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="8"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="5"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+    </row>
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="7"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1060,57 +1011,42 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="5"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1118,68 +1054,57 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="14.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="7.147857142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="14.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="G1" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="H1" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="I1" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="J1" t="s">
         <v>92</v>
       </c>
-      <c r="F1" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+    </row>
+    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1187,189 +1112,178 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="20.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="20.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="13.5703125" style="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="G1" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="H1" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="I1" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="J1" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="K1" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="L1" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="M1" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="I1" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="K1" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L1" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="M1" s="22" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5">
+    </row>
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>21</v>
       </c>
-      <c r="B2" s="23">
-        <v>1</v>
-      </c>
-      <c r="C2" s="23">
-        <v>1</v>
-      </c>
-      <c r="D2" s="23">
-        <v>1</v>
-      </c>
-      <c r="E2" s="23">
-        <v>0</v>
-      </c>
-      <c r="F2" s="23">
-        <v>0</v>
-      </c>
-      <c r="G2" s="23">
-        <v>0</v>
-      </c>
-      <c r="H2" s="23">
-        <v>0</v>
-      </c>
-      <c r="I2" s="23">
-        <v>0</v>
-      </c>
-      <c r="J2" s="23">
-        <v>0</v>
-      </c>
-      <c r="K2" s="23">
-        <v>0</v>
-      </c>
-      <c r="L2" s="23">
-        <v>0</v>
-      </c>
-      <c r="M2" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="5">
+      <c r="B2" s="18">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18">
+        <v>1</v>
+      </c>
+      <c r="D2" s="18">
+        <v>1</v>
+      </c>
+      <c r="E2" s="18">
+        <v>0</v>
+      </c>
+      <c r="F2" s="18">
+        <v>0</v>
+      </c>
+      <c r="G2" s="18">
+        <v>0</v>
+      </c>
+      <c r="H2" s="18">
+        <v>0</v>
+      </c>
+      <c r="I2" s="18">
+        <v>0</v>
+      </c>
+      <c r="J2" s="18">
+        <v>0</v>
+      </c>
+      <c r="K2" s="18">
+        <v>0</v>
+      </c>
+      <c r="L2" s="18">
+        <v>0</v>
+      </c>
+      <c r="M2" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>23</v>
       </c>
-      <c r="B3" s="23">
-        <v>1</v>
-      </c>
-      <c r="C3" s="23">
-        <v>1</v>
-      </c>
-      <c r="D3" s="23">
-        <v>1</v>
-      </c>
-      <c r="E3" s="23">
-        <v>0</v>
-      </c>
-      <c r="F3" s="23">
-        <v>0</v>
-      </c>
-      <c r="G3" s="23">
-        <v>0</v>
-      </c>
-      <c r="H3" s="23">
-        <v>0</v>
-      </c>
-      <c r="I3" s="23">
-        <v>0</v>
-      </c>
-      <c r="J3" s="23">
-        <v>0</v>
-      </c>
-      <c r="K3" s="23">
-        <v>0</v>
-      </c>
-      <c r="L3" s="23">
-        <v>0</v>
-      </c>
-      <c r="M3" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="5">
+      <c r="B3" s="18">
+        <v>1</v>
+      </c>
+      <c r="C3" s="18">
+        <v>1</v>
+      </c>
+      <c r="D3" s="18">
+        <v>1</v>
+      </c>
+      <c r="E3" s="18">
+        <v>0</v>
+      </c>
+      <c r="F3" s="18">
+        <v>0</v>
+      </c>
+      <c r="G3" s="18">
+        <v>0</v>
+      </c>
+      <c r="H3" s="18">
+        <v>0</v>
+      </c>
+      <c r="I3" s="18">
+        <v>0</v>
+      </c>
+      <c r="J3" s="18">
+        <v>0</v>
+      </c>
+      <c r="K3" s="18">
+        <v>0</v>
+      </c>
+      <c r="L3" s="18">
+        <v>0</v>
+      </c>
+      <c r="M3" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>24</v>
       </c>
-      <c r="B4" s="23">
-        <v>1</v>
-      </c>
-      <c r="C4" s="23">
-        <v>1</v>
-      </c>
-      <c r="D4" s="23">
-        <v>1</v>
-      </c>
-      <c r="E4" s="23">
-        <v>1e-9</v>
-      </c>
-      <c r="F4" s="23">
-        <v>1e-9</v>
-      </c>
-      <c r="G4" s="23">
-        <v>1e-9</v>
-      </c>
-      <c r="H4" s="23">
-        <v>0</v>
-      </c>
-      <c r="I4" s="23">
-        <v>0</v>
-      </c>
-      <c r="J4" s="23">
-        <v>0</v>
-      </c>
-      <c r="K4" s="23">
-        <v>0</v>
-      </c>
-      <c r="L4" s="23">
-        <v>0</v>
-      </c>
-      <c r="M4" s="23">
+      <c r="B4" s="18">
+        <v>1</v>
+      </c>
+      <c r="C4" s="18">
+        <v>1</v>
+      </c>
+      <c r="D4" s="18">
+        <v>1</v>
+      </c>
+      <c r="E4" s="18">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F4" s="18">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="G4" s="18">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H4" s="18">
+        <v>0</v>
+      </c>
+      <c r="I4" s="18">
+        <v>0</v>
+      </c>
+      <c r="J4" s="18">
+        <v>0</v>
+      </c>
+      <c r="K4" s="18">
+        <v>0</v>
+      </c>
+      <c r="L4" s="18">
+        <v>0</v>
+      </c>
+      <c r="M4" s="18">
         <v>0</v>
       </c>
     </row>
@@ -1379,110 +1293,87 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="10" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="21.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" style="9" customWidth="1"/>
+    <col min="3" max="4" width="6.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" style="9" customWidth="1"/>
+    <col min="6" max="10" width="6.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="20" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="D1" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="E1" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="G1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="H1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="I1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="J1" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="K1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="L1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="M1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="N1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="O1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="P1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="Q1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="R1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="Q1" s="21" t="s">
+      <c r="S1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="R1" s="21" t="s">
+      <c r="T1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="T1" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="U1" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="V1" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="W1" s="21" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="U1" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1543,13 +1434,7 @@
       <c r="T2" s="1">
         <v>0</v>
       </c>
-      <c r="U2" s="1">
-        <v>0</v>
-      </c>
-      <c r="V2" s="1">
-        <v>0</v>
-      </c>
-      <c r="W2" s="1">
+      <c r="U2" s="20">
         <v>0</v>
       </c>
     </row>
@@ -1559,279 +1444,279 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="13" width="34.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="20" width="12.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="18">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
+      <c r="B4" s="14">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="18">
-        <v>1e-10</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
+      <c r="B6" s="14">
+        <v>1E-10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
+      <c r="B8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
+      <c r="B9" s="14">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3" t="s">
+      <c r="B10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3" t="s">
+      <c r="B11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="18">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
+      <c r="B12" s="14">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="3" t="s">
+      <c r="B13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="18">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="3" t="s">
+      <c r="B15" s="14">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="18">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="3" t="s">
+      <c r="B16" s="14">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="3" t="s">
+      <c r="B17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="3" t="s">
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="3" t="s">
+      <c r="B19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="3" t="s">
+      <c r="B20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="3" t="s">
+      <c r="B21" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="3" t="s">
+      <c r="B22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="3" t="s">
+      <c r="B23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="3" t="s">
+      <c r="B24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="3" t="s">
+      <c r="B25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="3" t="s">
+      <c r="B26" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="3" t="s">
+      <c r="B27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="3" t="s">
+      <c r="B28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="3" t="s">
+      <c r="B29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="3" t="s">
+      <c r="B30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>49</v>
       </c>
-      <c r="B31" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="3" t="s">
+      <c r="B31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="3" t="s">
+      <c r="B32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="18">
-        <v>0.000001</v>
+      <c r="B33" s="14">
+        <v>9.9999999999999995E-7</v>
       </c>
     </row>
   </sheetData>
@@ -1840,78 +1725,78 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="13" width="23.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="11.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="18">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="14">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>1</v>
       </c>
     </row>
@@ -1921,80 +1806,72 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="16" width="11.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="15.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="17"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="17"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="17"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="17"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="17"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="17"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="17"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="17"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2002,110 +1879,97 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="16.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="17.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="16" width="12.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="16.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="5"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="5"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="5"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="5"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="5"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="5"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="5"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="5"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="5"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="5"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="5"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="5"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+    <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tests/3D_loop_cond_base/input_template.xlsx
+++ b/tests/3D_loop_cond_base/input_template.xlsx
@@ -1,30 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlasmaArc\tests\3D_loop_cond_base\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7213A11D-5048-493C-AC45-D2838AB72958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="element_types" sheetId="1" r:id="rId1"/>
-    <sheet name="cp" sheetId="2" r:id="rId2"/>
-    <sheet name="cpcyc" sheetId="3" r:id="rId3"/>
-    <sheet name="materials" sheetId="4" r:id="rId4"/>
-    <sheet name="real_constants" sheetId="5" r:id="rId5"/>
-    <sheet name="solver_settings" sheetId="6" r:id="rId6"/>
-    <sheet name="time_parameters" sheetId="7" r:id="rId7"/>
-    <sheet name="elem" sheetId="8" r:id="rId8"/>
-    <sheet name="node" sheetId="9" r:id="rId9"/>
-    <sheet name="transient_analysis" sheetId="10" r:id="rId10"/>
+    <sheet r:id="rId1" sheetId="1" name="element_types"/>
+    <sheet r:id="rId2" sheetId="2" name="cp"/>
+    <sheet r:id="rId3" sheetId="3" name="cpcyc"/>
+    <sheet r:id="rId4" sheetId="4" name="materials"/>
+    <sheet r:id="rId5" sheetId="5" name="real_constants"/>
+    <sheet r:id="rId6" sheetId="6" name="solver_settings"/>
+    <sheet r:id="rId7" sheetId="7" name="time_parameters"/>
+    <sheet r:id="rId8" sheetId="8" name="elem"/>
+    <sheet r:id="rId9" sheetId="9" name="node"/>
+    <sheet r:id="rId10" sheetId="10" name="transient_analysis"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -190,12 +184,18 @@
     <t>ansys_real_constant</t>
   </si>
   <si>
+    <t>THK</t>
+  </si>
+  <si>
     <t>SC</t>
   </si>
   <si>
     <t>NC</t>
   </si>
   <si>
+    <t>VC</t>
+  </si>
+  <si>
     <t>RAD</t>
   </si>
   <si>
@@ -241,6 +241,9 @@
     <t>ZLOC</t>
   </si>
   <si>
+    <t>CPSIGN</t>
+  </si>
+  <si>
     <t>ansys_material_type</t>
   </si>
   <si>
@@ -335,21 +338,12 @@
   </si>
   <si>
     <t>SOLID97</t>
-  </si>
-  <si>
-    <t>CPSIGN</t>
-  </si>
-  <si>
-    <t>THK</t>
-  </si>
-  <si>
-    <t>VC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
@@ -365,13 +359,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -403,76 +397,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="17">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -483,10 +466,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -524,71 +507,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -616,7 +599,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -639,11 +622,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -652,13 +635,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -668,7 +651,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -677,7 +660,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -686,7 +669,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -694,10 +677,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -762,107 +745,111 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="7" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="14.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="1">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="B2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="1">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="1">
         <v>3</v>
       </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="1">
         <v>4</v>
       </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -872,24 +859,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="7" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="22.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="16.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="19.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="21.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="10" width="21.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -899,111 +886,143 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5">
-        <v>1E-4</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.0001</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="2">
+        <v>0.0002</v>
+      </c>
+      <c r="C3" s="1">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="4"/>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="4"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
       <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="4"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
       <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
       <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="7"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
       <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="8"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
       <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="7"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
       <c r="F10" s="2"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1011,42 +1030,57 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="D1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1054,57 +1088,68 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="12" width="14.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="7.147857142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I1" t="s">
         <v>91</v>
       </c>
-      <c r="J1" t="s">
+      <c r="G1" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="H1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1112,178 +1157,189 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="13.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="7" width="20.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="C1" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="E1" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="F1" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="G1" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="H1" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="I1" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="J1" s="15" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="K1" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1">
         <v>21</v>
       </c>
-      <c r="B2" s="18">
-        <v>1</v>
-      </c>
-      <c r="C2" s="18">
-        <v>1</v>
-      </c>
-      <c r="D2" s="18">
-        <v>1</v>
-      </c>
-      <c r="E2" s="18">
-        <v>0</v>
-      </c>
-      <c r="F2" s="18">
-        <v>0</v>
-      </c>
-      <c r="G2" s="18">
-        <v>0</v>
-      </c>
-      <c r="H2" s="18">
-        <v>0</v>
-      </c>
-      <c r="I2" s="18">
-        <v>0</v>
-      </c>
-      <c r="J2" s="18">
-        <v>0</v>
-      </c>
-      <c r="K2" s="18">
-        <v>0</v>
-      </c>
-      <c r="L2" s="18">
-        <v>0</v>
-      </c>
-      <c r="M2" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="B2" s="15">
+        <v>1</v>
+      </c>
+      <c r="C2" s="15">
+        <v>1</v>
+      </c>
+      <c r="D2" s="15">
+        <v>1</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0</v>
+      </c>
+      <c r="H2" s="15">
+        <v>0</v>
+      </c>
+      <c r="I2" s="15">
+        <v>0</v>
+      </c>
+      <c r="J2" s="15">
+        <v>0</v>
+      </c>
+      <c r="K2" s="15">
+        <v>0</v>
+      </c>
+      <c r="L2" s="15">
+        <v>0</v>
+      </c>
+      <c r="M2" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1">
         <v>23</v>
       </c>
-      <c r="B3" s="18">
-        <v>1</v>
-      </c>
-      <c r="C3" s="18">
-        <v>1</v>
-      </c>
-      <c r="D3" s="18">
-        <v>1</v>
-      </c>
-      <c r="E3" s="18">
-        <v>0</v>
-      </c>
-      <c r="F3" s="18">
-        <v>0</v>
-      </c>
-      <c r="G3" s="18">
-        <v>0</v>
-      </c>
-      <c r="H3" s="18">
-        <v>0</v>
-      </c>
-      <c r="I3" s="18">
-        <v>0</v>
-      </c>
-      <c r="J3" s="18">
-        <v>0</v>
-      </c>
-      <c r="K3" s="18">
-        <v>0</v>
-      </c>
-      <c r="L3" s="18">
-        <v>0</v>
-      </c>
-      <c r="M3" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="B3" s="15">
+        <v>1</v>
+      </c>
+      <c r="C3" s="15">
+        <v>1</v>
+      </c>
+      <c r="D3" s="15">
+        <v>1</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15">
+        <v>0</v>
+      </c>
+      <c r="G3" s="15">
+        <v>0</v>
+      </c>
+      <c r="H3" s="15">
+        <v>0</v>
+      </c>
+      <c r="I3" s="15">
+        <v>0</v>
+      </c>
+      <c r="J3" s="15">
+        <v>0</v>
+      </c>
+      <c r="K3" s="15">
+        <v>0</v>
+      </c>
+      <c r="L3" s="15">
+        <v>0</v>
+      </c>
+      <c r="M3" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" s="18">
-        <v>1</v>
-      </c>
-      <c r="C4" s="18">
-        <v>1</v>
-      </c>
-      <c r="D4" s="18">
-        <v>1</v>
-      </c>
-      <c r="E4" s="18">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F4" s="18">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="G4" s="18">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H4" s="18">
-        <v>0</v>
-      </c>
-      <c r="I4" s="18">
-        <v>0</v>
-      </c>
-      <c r="J4" s="18">
-        <v>0</v>
-      </c>
-      <c r="K4" s="18">
-        <v>0</v>
-      </c>
-      <c r="L4" s="18">
-        <v>0</v>
-      </c>
-      <c r="M4" s="18">
+      <c r="B4" s="15">
+        <v>1</v>
+      </c>
+      <c r="C4" s="15">
+        <v>1</v>
+      </c>
+      <c r="D4" s="15">
+        <v>1</v>
+      </c>
+      <c r="E4" s="15">
+        <v>1e-9</v>
+      </c>
+      <c r="F4" s="15">
+        <v>1e-9</v>
+      </c>
+      <c r="G4" s="15">
+        <v>1e-9</v>
+      </c>
+      <c r="H4" s="15">
+        <v>0</v>
+      </c>
+      <c r="I4" s="15">
+        <v>0</v>
+      </c>
+      <c r="J4" s="15">
+        <v>0</v>
+      </c>
+      <c r="K4" s="15">
+        <v>0</v>
+      </c>
+      <c r="L4" s="15">
+        <v>0</v>
+      </c>
+      <c r="M4" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1293,87 +1349,102 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" style="9" customWidth="1"/>
-    <col min="3" max="4" width="6.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="9" customWidth="1"/>
-    <col min="6" max="10" width="6.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="20" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="7" width="21.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="21.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="9" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="G1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="H1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="I1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="J1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="K1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="L1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="M1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="N1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="O1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="P1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="Q1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="R1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1434,7 +1505,7 @@
       <c r="T2" s="1">
         <v>0</v>
       </c>
-      <c r="U2" s="20">
+      <c r="U2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1444,279 +1515,279 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="10" width="34.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="12.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="14">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B4" s="13">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="14">
-        <v>1E-10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B6" s="13">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="14">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B9" s="13">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="14">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B12" s="13">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="14">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B15" s="13">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="14">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B16" s="13">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B31" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="14">
-        <v>9.9999999999999995E-7</v>
+      <c r="B33" s="13">
+        <v>0.000001</v>
       </c>
     </row>
   </sheetData>
@@ -1725,78 +1796,78 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="10" width="23.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="11.290714285714287" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="14">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1806,24 +1877,24 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="12" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="11.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="11" t="s">
@@ -1833,45 +1904,53 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="11"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="11"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="11"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="11"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="11"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="11"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="11"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="11"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1879,24 +1958,24 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="12" width="16.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="17.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="12.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="11" t="s">
@@ -1906,70 +1985,83 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="1"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="1"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="1"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="1"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="1"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="1"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="1"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="1"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="1"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tests/3D_loop_cond_base/input_template.xlsx
+++ b/tests/3D_loop_cond_base/input_template.xlsx
@@ -1,24 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APEC-M\tests\3D_loop_cond_base\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC365FF1-8B15-4E2C-9CFD-C808CD0CAE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="element_types"/>
-    <sheet r:id="rId2" sheetId="2" name="cp"/>
-    <sheet r:id="rId3" sheetId="3" name="cpcyc"/>
-    <sheet r:id="rId4" sheetId="4" name="materials"/>
-    <sheet r:id="rId5" sheetId="5" name="real_constants"/>
-    <sheet r:id="rId6" sheetId="6" name="solver_settings"/>
-    <sheet r:id="rId7" sheetId="7" name="time_parameters"/>
-    <sheet r:id="rId8" sheetId="8" name="elem"/>
-    <sheet r:id="rId9" sheetId="9" name="node"/>
-    <sheet r:id="rId10" sheetId="10" name="transient_analysis"/>
+    <sheet name="element_types" sheetId="1" r:id="rId1"/>
+    <sheet name="cp" sheetId="2" r:id="rId2"/>
+    <sheet name="cpcyc" sheetId="3" r:id="rId3"/>
+    <sheet name="materials" sheetId="4" r:id="rId4"/>
+    <sheet name="real_constants" sheetId="5" r:id="rId5"/>
+    <sheet name="solver_settings" sheetId="6" r:id="rId6"/>
+    <sheet name="time_parameters" sheetId="7" r:id="rId7"/>
+    <sheet name="elem" sheetId="8" r:id="rId8"/>
+    <sheet name="node" sheetId="9" r:id="rId9"/>
+    <sheet name="transient_analysis" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -343,7 +349,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
@@ -397,65 +403,60 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -466,10 +467,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -507,71 +508,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -599,7 +600,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -622,11 +623,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -635,13 +636,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -651,7 +652,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -660,7 +661,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -669,7 +670,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -677,10 +678,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -745,27 +746,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="14.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -784,11 +781,11 @@
         <v>103</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>21</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>104</v>
       </c>
       <c r="C2" s="1">
@@ -807,11 +804,11 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row r="3" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>23</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>104</v>
       </c>
       <c r="C3" s="1">
@@ -830,15 +827,15 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>104</v>
       </c>
       <c r="C4" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -859,24 +856,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="18.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="22.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="16.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="19.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="21.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="21.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="18.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -886,143 +883,115 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>0.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>0.0002</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    </row>
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    </row>
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    </row>
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="C7" s="4"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    </row>
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="4"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    </row>
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="4"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    </row>
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="4"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1030,57 +999,42 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    </row>
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    </row>
+    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1088,68 +1042,57 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="14.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="7.147857142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="14.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>94</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
       <c r="C2" s="2"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1157,189 +1100,178 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="20.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="20.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="13.5703125" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="13" t="s">
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>21</v>
       </c>
-      <c r="B2" s="15">
-        <v>1</v>
-      </c>
-      <c r="C2" s="15">
-        <v>1</v>
-      </c>
-      <c r="D2" s="15">
-        <v>1</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0</v>
-      </c>
-      <c r="H2" s="15">
-        <v>0</v>
-      </c>
-      <c r="I2" s="15">
-        <v>0</v>
-      </c>
-      <c r="J2" s="15">
-        <v>0</v>
-      </c>
-      <c r="K2" s="15">
-        <v>0</v>
-      </c>
-      <c r="L2" s="15">
-        <v>0</v>
-      </c>
-      <c r="M2" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="B2" s="13">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13">
+        <v>1</v>
+      </c>
+      <c r="D2" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0</v>
+      </c>
+      <c r="H2" s="13">
+        <v>0</v>
+      </c>
+      <c r="I2" s="13">
+        <v>0</v>
+      </c>
+      <c r="J2" s="13">
+        <v>0</v>
+      </c>
+      <c r="K2" s="13">
+        <v>0</v>
+      </c>
+      <c r="L2" s="13">
+        <v>0</v>
+      </c>
+      <c r="M2" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>23</v>
       </c>
-      <c r="B3" s="15">
-        <v>1</v>
-      </c>
-      <c r="C3" s="15">
-        <v>1</v>
-      </c>
-      <c r="D3" s="15">
-        <v>1</v>
-      </c>
-      <c r="E3" s="15">
-        <v>0</v>
-      </c>
-      <c r="F3" s="15">
-        <v>0</v>
-      </c>
-      <c r="G3" s="15">
-        <v>0</v>
-      </c>
-      <c r="H3" s="15">
-        <v>0</v>
-      </c>
-      <c r="I3" s="15">
-        <v>0</v>
-      </c>
-      <c r="J3" s="15">
-        <v>0</v>
-      </c>
-      <c r="K3" s="15">
-        <v>0</v>
-      </c>
-      <c r="L3" s="15">
-        <v>0</v>
-      </c>
-      <c r="M3" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="B3" s="13">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13">
+        <v>1</v>
+      </c>
+      <c r="D3" s="13">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0</v>
+      </c>
+      <c r="F3" s="13">
+        <v>0</v>
+      </c>
+      <c r="G3" s="13">
+        <v>0</v>
+      </c>
+      <c r="H3" s="13">
+        <v>0</v>
+      </c>
+      <c r="I3" s="13">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13">
+        <v>0</v>
+      </c>
+      <c r="K3" s="13">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13">
+        <v>0</v>
+      </c>
+      <c r="M3" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" s="15">
-        <v>1</v>
-      </c>
-      <c r="C4" s="15">
-        <v>1</v>
-      </c>
-      <c r="D4" s="15">
-        <v>1</v>
-      </c>
-      <c r="E4" s="15">
-        <v>1e-9</v>
-      </c>
-      <c r="F4" s="15">
-        <v>1e-9</v>
-      </c>
-      <c r="G4" s="15">
-        <v>1e-9</v>
-      </c>
-      <c r="H4" s="15">
-        <v>0</v>
-      </c>
-      <c r="I4" s="15">
-        <v>0</v>
-      </c>
-      <c r="J4" s="15">
-        <v>0</v>
-      </c>
-      <c r="K4" s="15">
-        <v>0</v>
-      </c>
-      <c r="L4" s="15">
-        <v>0</v>
-      </c>
-      <c r="M4" s="15">
+      <c r="B4" s="13">
+        <v>1</v>
+      </c>
+      <c r="C4" s="13">
+        <v>1</v>
+      </c>
+      <c r="D4" s="13">
+        <v>1</v>
+      </c>
+      <c r="E4" s="13">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F4" s="13">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="G4" s="13">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H4" s="13">
+        <v>0</v>
+      </c>
+      <c r="I4" s="13">
+        <v>0</v>
+      </c>
+      <c r="J4" s="13">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13">
+        <v>0</v>
+      </c>
+      <c r="M4" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1349,37 +1281,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="2" width="21.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="6.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -1444,7 +1358,7 @@
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1515,279 +1429,279 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="34.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="14" width="12.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="13">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
+      <c r="B4" s="11">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="1">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="13">
-        <v>1e-10</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
+      <c r="B6" s="11">
+        <v>1E-10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="13">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
+      <c r="B9" s="11">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="13">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
+      <c r="B12" s="11">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="1">
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="13">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="3" t="s">
+      <c r="B15" s="11">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="13">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="3" t="s">
+      <c r="B16" s="11">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>36</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>37</v>
       </c>
       <c r="B19" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>38</v>
       </c>
       <c r="B20" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>39</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>40</v>
       </c>
       <c r="B22" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>41</v>
       </c>
       <c r="B23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>42</v>
       </c>
       <c r="B24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="3" t="s">
+    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>43</v>
       </c>
       <c r="B25" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>44</v>
       </c>
       <c r="B26" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>45</v>
       </c>
       <c r="B27" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>46</v>
       </c>
       <c r="B28" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>47</v>
       </c>
       <c r="B29" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>48</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>49</v>
       </c>
       <c r="B31" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>50</v>
       </c>
       <c r="B32" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="3" t="s">
+    <row r="33" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="13">
-        <v>0.000001</v>
+      <c r="B33" s="11">
+        <v>9.9999999999999995E-7</v>
       </c>
     </row>
   </sheetData>
@@ -1796,75 +1710,75 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="23.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="11.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="13">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1">
@@ -1877,78 +1791,70 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="11.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="15.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="11"/>
-      <c r="B2" s="3"/>
+    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="11"/>
-      <c r="B3" s="3"/>
+    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="11"/>
-      <c r="B4" s="3"/>
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="11"/>
-      <c r="B5" s="3"/>
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="11"/>
-      <c r="B6" s="3"/>
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="11"/>
-      <c r="B7" s="3"/>
+    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="11"/>
-      <c r="B8" s="3"/>
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="11"/>
-      <c r="B9" s="3"/>
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
@@ -1958,108 +1864,95 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="12" width="16.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="17.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="12.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="16.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="3"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row r="4" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="3"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row r="5" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="3"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row r="6" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="3"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row r="7" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="3"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+    <row r="8" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="3"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+    <row r="9" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="3"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+    <row r="10" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+    <row r="11" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="3"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+    <row r="12" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="3"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+    <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="3"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+    <row r="14" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="3"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>

--- a/tests/3D_loop_cond_base/input_template.xlsx
+++ b/tests/3D_loop_cond_base/input_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APEC-M\tests\3D_loop_cond_base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC365FF1-8B15-4E2C-9CFD-C808CD0CAE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAC92B4-ED4A-4EF4-8237-04E54132D466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="element_types" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="106">
   <si>
     <t>time_step_number</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>SOLID97</t>
+  </si>
+  <si>
+    <t>CURR</t>
   </si>
 </sst>
 </file>
@@ -403,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -443,6 +446,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1285,7 +1291,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="21.140625" style="6" bestFit="1" customWidth="1"/>
@@ -1293,7 +1299,7 @@
     <col min="11" max="21" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -1357,8 +1363,11 @@
       <c r="U1" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V1" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1420,6 +1429,9 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="V2" s="15">
         <v>0</v>
       </c>
     </row>

--- a/tests/3D_loop_cond_base/input_template.xlsx
+++ b/tests/3D_loop_cond_base/input_template.xlsx
@@ -677,22 +677,22 @@
         <v>1</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -709,22 +709,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -750,13 +750,13 @@
         <v>1e-09</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/tests/3D_loop_cond_base/input_template.xlsx
+++ b/tests/3D_loop_cond_base/input_template.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="element_types" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,29 +19,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.000000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
-  </numFmts>
-  <fonts count="3">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -51,14 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -68,43 +47,13 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -183,34 +132,34 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="0000FF"/>
@@ -224,71 +173,69 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -312,53 +259,54 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -368,7 +316,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -377,7 +325,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -386,7 +334,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -394,10 +342,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -426,7 +374,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -439,12 +387,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -464,613 +413,539 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13.29071428571429" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
-    <col width="14.86214285714286" bestFit="1" customWidth="1" style="9" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="5" max="5"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="6" max="6"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TYPE_ID</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ELEMENT_TYPE</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>OPTION1</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OPTION2</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>OPTION3</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>OPTION4</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>OPTION5</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="3" t="n">
+    <row r="2">
+      <c r="A2" t="n">
         <v>21</v>
       </c>
-      <c r="B2" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>23</v>
       </c>
-      <c r="B3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="3" t="n">
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>24</v>
       </c>
-      <c r="B4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20.14785714285714" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="9" max="9"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="8" min="10" max="10"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>MATERIAL_ID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MUR_X</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MUR_Y</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MUR_Z</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>RHO_X</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>RHO_Y</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>RHO_Z</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>M_X</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>M_Y</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>M_Z</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="3" t="n">
+    <row r="2">
+      <c r="A2" t="n">
         <v>21</v>
       </c>
-      <c r="B2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>23</v>
       </c>
-      <c r="B3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="3" t="n">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>24</v>
       </c>
-      <c r="B4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7" t="n">
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>1e-09</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" t="n">
         <v>1e-09</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" t="n">
         <v>1e-09</v>
       </c>
-      <c r="H4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>1</v>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21.14785714285714" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
-    <col width="21.14785714285714" bestFit="1" customWidth="1" style="9" min="2" max="2"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="9" min="3" max="3"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="9" min="4" max="4"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="9" min="5" max="5"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="9" min="6" max="6"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="9" min="7" max="7"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="9" min="8" max="8"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="9" min="9" max="9"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="9" min="10" max="10"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="11" max="11"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="12" max="12"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="13" max="13"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="14" max="14"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="15" max="15"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="16" max="16"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="17" max="17"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="18" max="18"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="19" max="19"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="9" min="20" max="20"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CONSTANTS_ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>THK</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TURNS</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>VOL</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>T_X</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>T_Y</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>T_Z</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>V_X</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>V_Y</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>V_Z</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>OMEGA_X</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>OMEGA_Y</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>OMEGA_Z</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>LOC_X</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>LOC_Y</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LOC_Z</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="3" t="n">
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="12.14785714285714" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SETTING</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>VALUE</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ksp_type</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>preonly</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>pc_type</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>lu</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>initial_linear_tolerance</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" t="n">
         <v>1e-06</v>
       </c>
     </row>
-    <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>max_linear_iterations</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>minimum_linear_tolerance</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" t="n">
         <v>1e-10</v>
       </c>
     </row>
-    <row r="7" ht="19.5" customHeight="1"/>
-    <row r="8" ht="19.5" customHeight="1"/>
-    <row r="9" ht="19.5" customHeight="1"/>
-    <row r="10" ht="19.5" customHeight="1"/>
-    <row r="11" ht="19.5" customHeight="1"/>
-    <row r="12" ht="19.5" customHeight="1"/>
-    <row r="13" ht="19.5" customHeight="1"/>
-    <row r="14" ht="19.5" customHeight="1"/>
-    <row r="15" ht="19.5" customHeight="1"/>
-    <row r="16" ht="19.5" customHeight="1"/>
-    <row r="17" ht="19.5" customHeight="1"/>
-    <row r="18" ht="19.5" customHeight="1"/>
-    <row r="19" ht="18.75" customHeight="1"/>
-    <row r="20" ht="18.75" customHeight="1"/>
-    <row r="21" ht="18.75" customHeight="1"/>
-    <row r="22" ht="18.75" customHeight="1"/>
-    <row r="23" ht="18.75" customHeight="1"/>
-    <row r="24" ht="18.75" customHeight="1"/>
-    <row r="25" ht="18.75" customHeight="1"/>
-    <row r="26" ht="18.75" customHeight="1"/>
-    <row r="27" ht="18.75" customHeight="1"/>
-    <row r="28" ht="18.75" customHeight="1"/>
-    <row r="29" ht="18.75" customHeight="1"/>
-    <row r="30" ht="18.75" customHeight="1"/>
-    <row r="31" ht="18.75" customHeight="1"/>
-    <row r="32" ht="18.75" customHeight="1"/>
-    <row r="33" ht="18.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>